--- a/tests/Import/fixtures/01_codigos_de_proveedor.xlsx
+++ b/tests/Import/fixtures/01_codigos_de_proveedor.xlsx
@@ -95,6 +95,11 @@
       </c>
     </row>
     <row r="2" spans="1:8" customHeight="0">
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>SKU-NUEVO-UNICO</t>
+        </is>
+      </c>
       <c r="C2" s="0" t="inlineStr">
         <is>
           <t>PC-100</t>
@@ -121,6 +126,11 @@
       </c>
     </row>
     <row r="3" spans="1:8" customHeight="0">
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>SKU-NUEVO-DUP</t>
+        </is>
+      </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
           <t>PC-DUP</t>
